--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N119_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N119_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.58804054179717</v>
+        <v>10.98305658804204</v>
       </c>
       <c r="D2" t="n">
-        <v>69.32329186225358</v>
+        <v>11.26503492761621</v>
       </c>
       <c r="E2" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F2" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.23055735219794</v>
+        <v>3.287465569732166</v>
       </c>
       <c r="D3" t="n">
-        <v>20.33687812027057</v>
+        <v>3.304742694543967</v>
       </c>
       <c r="E3" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F3" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.82668074310337</v>
+        <v>4.359335620754298</v>
       </c>
       <c r="D4" t="n">
-        <v>28.46356341284167</v>
+        <v>4.62532905458677</v>
       </c>
       <c r="E4" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F4" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.5644307785691</v>
+        <v>8.216720001517478</v>
       </c>
       <c r="D5" t="n">
-        <v>50.30762477175493</v>
+        <v>8.174989025410177</v>
       </c>
       <c r="E5" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F5" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.09103819522301</v>
+        <v>10.57729370672374</v>
       </c>
       <c r="D6" t="n">
-        <v>64.9288240992822</v>
+        <v>10.55093391613336</v>
       </c>
       <c r="E6" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F6" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.77414986191881</v>
+        <v>4.838299352561807</v>
       </c>
       <c r="D7" t="n">
-        <v>28.93847482189254</v>
+        <v>4.702502158557539</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F7" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.3348346424325</v>
+        <v>6.066910629395281</v>
       </c>
       <c r="D8" t="n">
-        <v>37.13528579391957</v>
+        <v>6.03448394151193</v>
       </c>
       <c r="E8" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F8" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.684461858847547</v>
+        <v>1.411225052062726</v>
       </c>
       <c r="D9" t="n">
-        <v>8.552198270257056</v>
+        <v>1.389732218916772</v>
       </c>
       <c r="E9" t="n">
-        <v>19.79519258405903</v>
+        <v>3.216718794909593</v>
       </c>
       <c r="F9" t="n">
-        <v>20.02736607764605</v>
+        <v>3.254446987617484</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
